--- a/docs/ops-workbench-us-v2.xlsx
+++ b/docs/ops-workbench-us-v2.xlsx
@@ -18,7 +18,7 @@
     <sheet name="本轮补漏" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'User Stories'!$A$1:$L$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'User Stories'!$A$1:$L$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'性能与安全（NFR）'!$A$1:$H$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">本轮补漏!$A$1:$F$48</definedName>
   </definedNames>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="435">
   <si>
     <t>US编号</t>
   </si>
@@ -1031,6 +1031,28 @@
   </si>
   <si>
     <t>链接格式、是否可外网打开</t>
+  </si>
+  <si>
+    <t>US-45</t>
+  </si>
+  <si>
+    <t>业务系统详情页嵌入任务视图时，只露中间区与右侧栏，右侧默认抽屉</t>
+  </si>
+  <si>
+    <t>作为处理人，我希望在业务系统详情页里直接处理工作台任务时，只看到中间处理区和右侧上下文，并且右侧默认以抽屉叠层出现，同时也支持在宿主页面里把中间区留给办理，需要时再拉开详情。</t>
+  </si>
+  <si>
+    <t>例如从 PACE 一类业务系统的任务详情进入：工作台被嵌在宿主页内，隐藏工作台自身左栏和顶栏，只保留 Task 中间栏与右侧上下文。右侧默认是抽屉（叠在中间上、不永久分栏挤占），可收起后再展开。与 US-46 的关系：US-46 是独立打开工作台时的宽屏分栏 / 窄屏抽屉；本条是被宿主嵌入时的布局，不随宿主窗口宽窄改成并排分栏。与 US-15 的关系：US-15 是独立工作台左侧导航收起。进出宿主、返回列表不在本条。</t>
+  </si>
+  <si>
+    <t>1. 工作台任务视图被嵌入业务系统详情页后，只展示中间处理区与右侧上下文；工作台自身左侧导航和顶栏不出现。
+2. 嵌入态下右侧上下文默认以抽屉叠层呈现：向左展开时叠在中间区上，不改为与中间永久分栏挤占宽度。
+3. 右侧抽屉可收起；收起后中间区被让出，并保留再次展开的入口。
+4. 展开/收起后仍绑定同一工作项上下文（与 US-04、US-05 一致）。
+5. 同一工作台在独立打开时仍按 US-46（宽屏分栏 / 窄屏抽屉），不与本条的嵌入抽屉互相覆盖。</t>
+  </si>
+  <si>
+    <t>用何种技术嵌入（如 iframe）、宿主页自己的顶栏/表单/按钮、右侧各页签的业务内容、抽屉默认展开还是收起的像素与动效、独立工作台的宽窄断点（归 US-46）</t>
   </si>
   <si>
     <t>US-46</t>
@@ -1716,6 +1738,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1801,12 +1829,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2046,7 +2068,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2070,16 +2092,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2088,42 +2110,42 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2170,7 +2192,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2240,6 +2262,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2625,7 +2653,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
@@ -2633,8 +2661,8 @@
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="7" max="7" width="16.0363636363636" customWidth="1"/>
+    <col min="8" max="8" width="11.5454545454545" customWidth="1"/>
     <col min="9" max="10" width="48" customWidth="1"/>
     <col min="11" max="11" width="56" customWidth="1"/>
     <col min="12" max="12" width="36" customWidth="1"/>
@@ -4388,8 +4416,8 @@
         <v>293</v>
       </c>
     </row>
-    <row r="47" s="2" customFormat="1" ht="76" customHeight="1" spans="1:12">
-      <c r="A47" s="13" t="s">
+    <row r="47" s="2" customFormat="1" ht="154" customHeight="1" spans="1:12">
+      <c r="A47" s="25" t="s">
         <v>294</v>
       </c>
       <c r="B47" s="13" t="s">
@@ -4398,14 +4426,14 @@
       <c r="C47" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="26" t="s">
         <v>295</v>
       </c>
       <c r="E47" s="21" t="s">
         <v>23</v>
       </c>
       <c r="F47" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>104</v>
@@ -4436,7 +4464,7 @@
       <c r="C48" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D48" s="24" t="s">
+      <c r="D48" s="15" t="s">
         <v>301</v>
       </c>
       <c r="E48" s="21" t="s">
@@ -4464,7 +4492,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="49" s="2" customFormat="1" ht="92" customHeight="1" spans="1:12">
+    <row r="49" s="2" customFormat="1" ht="76" customHeight="1" spans="1:12">
       <c r="A49" s="13" t="s">
         <v>306</v>
       </c>
@@ -4510,19 +4538,19 @@
         <v>36</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D50" s="24" t="s">
         <v>313</v>
       </c>
-      <c r="E50" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="16">
-        <v>0</v>
+      <c r="E50" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F50" s="14">
+        <v>1</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="H50" s="13" t="s">
         <v>39</v>
@@ -4540,8 +4568,46 @@
         <v>317</v>
       </c>
     </row>
+    <row r="51" s="2" customFormat="1" ht="92" customHeight="1" spans="1:12">
+      <c r="A51" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="16">
+        <v>0</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>323</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L50" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L51" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4562,10 +4628,10 @@
   <sheetData>
     <row r="1" s="17" customFormat="1" ht="22" customHeight="1" spans="1:2">
       <c r="A1" s="17" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
@@ -4573,7 +4639,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
@@ -4581,15 +4647,15 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
@@ -4597,87 +4663,87 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="36" customHeight="1" spans="1:2">
       <c r="A15" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -4703,7 +4769,7 @@
   <sheetData>
     <row r="1" s="11" customFormat="1" ht="22" customHeight="1" spans="1:8">
       <c r="A1" s="12" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B1" s="12" t="s">
         <v>1</v>
@@ -4715,7 +4781,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>10</v>
@@ -4724,137 +4790,137 @@
         <v>11</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="48" customHeight="1" spans="1:8">
       <c r="A2" s="13" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="G2" s="13" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A3" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>356</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>350</v>
-      </c>
       <c r="D3" s="15" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A4" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>370</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="H4" s="13" t="s">
         <v>361</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>350</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>362</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="48" customHeight="1" spans="1:8">
       <c r="A5" s="13" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A6" s="13" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -4885,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -4897,7 +4963,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -4905,7 +4971,7 @@
         <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>15</v>
@@ -4917,7 +4983,7 @@
         <v>58</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -4925,7 +4991,7 @@
         <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>15</v>
@@ -4937,7 +5003,7 @@
         <v>70</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -4945,7 +5011,7 @@
         <v>81</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>15</v>
@@ -4957,7 +5023,7 @@
         <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -4965,7 +5031,7 @@
         <v>87</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>15</v>
@@ -4977,7 +5043,7 @@
         <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -4985,7 +5051,7 @@
         <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>23</v>
@@ -4997,7 +5063,7 @@
         <v>128</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5005,7 +5071,7 @@
         <v>168</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>15</v>
@@ -5017,7 +5083,7 @@
         <v>169</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5025,7 +5091,7 @@
         <v>174</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>15</v>
@@ -5037,7 +5103,7 @@
         <v>175</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5045,7 +5111,7 @@
         <v>180</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>15</v>
@@ -5057,7 +5123,7 @@
         <v>181</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5065,7 +5131,7 @@
         <v>186</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>15</v>
@@ -5077,7 +5143,7 @@
         <v>187</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5085,7 +5151,7 @@
         <v>192</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>15</v>
@@ -5097,7 +5163,7 @@
         <v>193</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5105,7 +5171,7 @@
         <v>198</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>15</v>
@@ -5117,7 +5183,7 @@
         <v>199</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5125,7 +5191,7 @@
         <v>204</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>15</v>
@@ -5137,7 +5203,7 @@
         <v>205</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5145,7 +5211,7 @@
         <v>210</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>15</v>
@@ -5157,7 +5223,7 @@
         <v>211</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5165,7 +5231,7 @@
         <v>216</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>23</v>
@@ -5177,7 +5243,7 @@
         <v>217</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5185,7 +5251,7 @@
         <v>222</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>23</v>
@@ -5197,7 +5263,7 @@
         <v>223</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5205,7 +5271,7 @@
         <v>228</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>23</v>
@@ -5217,7 +5283,7 @@
         <v>229</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5225,7 +5291,7 @@
         <v>234</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>23</v>
@@ -5237,7 +5303,7 @@
         <v>235</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5245,7 +5311,7 @@
         <v>240</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>23</v>
@@ -5257,7 +5323,7 @@
         <v>241</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5265,7 +5331,7 @@
         <v>246</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>23</v>
@@ -5277,7 +5343,7 @@
         <v>247</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5285,7 +5351,7 @@
         <v>252</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>23</v>
@@ -5297,7 +5363,7 @@
         <v>253</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5305,7 +5371,7 @@
         <v>258</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>30</v>
@@ -5317,7 +5383,7 @@
         <v>259</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5325,7 +5391,7 @@
         <v>109</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>23</v>
@@ -5337,7 +5403,7 @@
         <v>110</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5345,7 +5411,7 @@
         <v>75</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>15</v>
@@ -5357,7 +5423,7 @@
         <v>76</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5365,7 +5431,7 @@
         <v>174</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>15</v>
@@ -5377,7 +5443,7 @@
         <v>175</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5385,7 +5451,7 @@
         <v>87</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>15</v>
@@ -5397,7 +5463,7 @@
         <v>88</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5405,7 +5471,7 @@
         <v>127</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>23</v>
@@ -5417,7 +5483,7 @@
         <v>128</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5425,7 +5491,7 @@
         <v>81</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>15</v>
@@ -5437,7 +5503,7 @@
         <v>82</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5445,7 +5511,7 @@
         <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>15</v>
@@ -5457,7 +5523,7 @@
         <v>45</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5465,7 +5531,7 @@
         <v>63</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>15</v>
@@ -5477,7 +5543,7 @@
         <v>64</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5485,7 +5551,7 @@
         <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>15</v>
@@ -5497,7 +5563,7 @@
         <v>70</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5505,7 +5571,7 @@
         <v>121</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>23</v>
@@ -5517,7 +5583,7 @@
         <v>122</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5525,7 +5591,7 @@
         <v>168</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>15</v>
@@ -5537,7 +5603,7 @@
         <v>169</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5545,7 +5611,7 @@
         <v>228</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>23</v>
@@ -5557,7 +5623,7 @@
         <v>229</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5565,7 +5631,7 @@
         <v>246</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>23</v>
@@ -5577,7 +5643,7 @@
         <v>247</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="36" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5585,7 +5651,7 @@
         <v>51</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>15</v>
@@ -5597,7 +5663,7 @@
         <v>52</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="37" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5605,7 +5671,7 @@
         <v>174</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>15</v>
@@ -5617,7 +5683,7 @@
         <v>175</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="38" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5625,7 +5691,7 @@
         <v>186</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>15</v>
@@ -5637,7 +5703,7 @@
         <v>187</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5645,7 +5711,7 @@
         <v>264</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>15</v>
@@ -5657,7 +5723,7 @@
         <v>265</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="40" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5665,7 +5731,7 @@
         <v>270</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>15</v>
@@ -5677,7 +5743,7 @@
         <v>271</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="41" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5685,7 +5751,7 @@
         <v>276</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>15</v>
@@ -5697,7 +5763,7 @@
         <v>277</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="42" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5705,7 +5771,7 @@
         <v>282</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>30</v>
@@ -5717,7 +5783,7 @@
         <v>283</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
@@ -5725,7 +5791,7 @@
         <v>288</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>23</v>
@@ -5737,15 +5803,15 @@
         <v>289</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
       <c r="A44" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>23</v>
@@ -5754,18 +5820,18 @@
         <v>1</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
       <c r="A45" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>23</v>
@@ -5774,18 +5840,18 @@
         <v>1</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>23</v>
@@ -5794,18 +5860,18 @@
         <v>1</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="47" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
       <c r="A47" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>15</v>
@@ -5814,30 +5880,30 @@
         <v>0</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="48" s="2" customFormat="1" ht="32" customHeight="1" spans="1:6">
       <c r="A48" s="9" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D48" s="4">
         <v>0</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
   </sheetData>
